--- a/hypatia/examples/Atlantis/parameters/parameters_reg1.xlsx
+++ b/hypatia/examples/Atlantis/parameters/parameters_reg1.xlsx
@@ -1851,16 +1851,16 @@
         <v>29</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/hypatia/examples/Atlantis/parameters/parameters_reg1.xlsx
+++ b/hypatia/examples/Atlantis/parameters/parameters_reg1.xlsx
@@ -1851,16 +1851,16 @@
         <v>29</v>
       </c>
       <c r="B4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
